--- a/backend/plantillas/plantilla_estudiantes.xlsx
+++ b/backend/plantillas/plantilla_estudiantes.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>cedula de ciudadania</t>
+          <t>C.C.</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -533,7 +533,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cedula de ciudadania</t>
+          <t>C.C.</t>
         </is>
       </c>
       <c r="F3" t="n">
